--- a/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,31</t>
+          <t>4,76; 12,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 9,03</t>
+          <t>0,6; 9,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -0,63</t>
+          <t>-10,99; -0,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,17</t>
+          <t>3,54; 9,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,77</t>
+          <t>1,96; 8,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,23; -6,57</t>
+          <t>-13,26; -6,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,95</t>
+          <t>5,21; 10,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,74</t>
+          <t>2,75; 7,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -4,9</t>
+          <t>-10,49; -4,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 18,43</t>
+          <t>6,74; 18,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 13,65</t>
+          <t>0,83; 13,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -1,03</t>
+          <t>-15,56; -1,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 11,55</t>
+          <t>4,17; 11,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,11</t>
+          <t>2,37; 10,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,15; -8,33</t>
+          <t>-16,23; -8,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 13,44</t>
+          <t>6,86; 13,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,45</t>
+          <t>3,6; 10,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,96; -6,58</t>
+          <t>-13,63; -6,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,05</t>
+          <t>5,52; 12,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 12,37</t>
+          <t>5,96; 12,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 0,76</t>
+          <t>-14,46; 0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,6</t>
+          <t>2,42; 9,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,94</t>
+          <t>0,25; 7,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 6,61</t>
+          <t>-15,44; 7,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,24</t>
+          <t>4,91; 9,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,03</t>
+          <t>4,12; 9,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 2,4</t>
+          <t>-12,77; 1,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 32,72</t>
+          <t>13,93; 33,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,26; 33,8</t>
+          <t>14,52; 35,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 1,97</t>
+          <t>-38,57; 1,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 18,48</t>
+          <t>4,43; 18,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 13,63</t>
+          <t>0,45; 13,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 12,54</t>
+          <t>-28,25; 14,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 20,69</t>
+          <t>10,52; 21,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 20,18</t>
+          <t>8,77; 20,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 5,28</t>
+          <t>-27,37; 3,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,4</t>
+          <t>0,81; 14,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 7,52</t>
+          <t>-5,07; 7,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -0,26</t>
+          <t>-12,29; -0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 8,86</t>
+          <t>-4,75; 8,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 1,79</t>
+          <t>-10,55; 2,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,23; -11,17</t>
+          <t>-22,52; -11,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 9,86</t>
+          <t>0,56; 10,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 3,33</t>
+          <t>-5,3; 3,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -6,97</t>
+          <t>-15,45; -7,52</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 39,26</t>
+          <t>1,84; 39,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 21,02</t>
+          <t>-11,96; 20,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,25; -0,33</t>
+          <t>-29,06; -2,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 17,87</t>
+          <t>-8,77; 16,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 3,53</t>
+          <t>-19,19; 3,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,46; -22,87</t>
+          <t>-40,37; -23,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 22,94</t>
+          <t>1,21; 23,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 7,69</t>
+          <t>-11,3; 7,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,63; -16,31</t>
+          <t>-32,22; -17,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,74</t>
+          <t>5,11; 9,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,78</t>
+          <t>1,57; 6,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -5,88</t>
+          <t>-18,33; -6,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,67</t>
+          <t>3,12; 7,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,32</t>
+          <t>-2,36; 2,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,58; -4,87</t>
+          <t>-19,54; -4,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,19</t>
+          <t>4,77; 8,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,85</t>
+          <t>0,26; 3,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -7,74</t>
+          <t>-17,17; -8,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,86; 20,85</t>
+          <t>10,46; 21,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 14,47</t>
+          <t>3,16; 14,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,16; -12,33</t>
+          <t>-37,35; -12,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,35</t>
+          <t>4,79; 12,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,69</t>
+          <t>-3,6; 3,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,37; -7,65</t>
+          <t>-30,36; -6,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,25; 14,83</t>
+          <t>8,35; 14,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,98</t>
+          <t>0,44; 6,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,06; -13,76</t>
+          <t>-30,58; -14,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>-9,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,96</t>
+          <t>-10,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-9,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 12,18</t>
+          <t>4,59; 12,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 9,2</t>
+          <t>0,2; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -0,94</t>
+          <t>-14,48; -4,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,25</t>
+          <t>3,68; 9,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,32</t>
+          <t>2,64; 8,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; -6,73</t>
+          <t>-14,2; -7,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 10,04</t>
+          <t>5,01; 9,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,76</t>
+          <t>2,53; 7,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,49; -4,85</t>
+          <t>-12,78; -7,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-8,25%</t>
+          <t>-13,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,34%</t>
+          <t>-13,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,34%</t>
+          <t>-13,18%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 18,51</t>
+          <t>6,43; 19,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 13,59</t>
+          <t>0,32; 13,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -1,33</t>
+          <t>-20,92; -6,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 11,72</t>
+          <t>4,5; 11,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,47</t>
+          <t>3,16; 10,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,23; -8,59</t>
+          <t>-17,38; -9,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 13,7</t>
+          <t>6,63; 13,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,43</t>
+          <t>3,27; 10,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -6,56</t>
+          <t>-16,67; -9,5</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-1,68</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,18</t>
+          <t>-12,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-6,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 12,07</t>
+          <t>5,27; 12,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,79</t>
+          <t>6,29; 12,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 0,46</t>
+          <t>-4,63; 1,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,4</t>
+          <t>2,57; 9,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 7,21</t>
+          <t>0,32; 7,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 7,07</t>
+          <t>-15,45; -9,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,68</t>
+          <t>4,8; 9,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,11</t>
+          <t>4,28; 8,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 1,62</t>
+          <t>-9,16; -4,47</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,86%</t>
+          <t>-4,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-15,37%</t>
+          <t>-22,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-13,59%</t>
+          <t>-14,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,93; 33,52</t>
+          <t>13,4; 33,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 35,11</t>
+          <t>15,66; 35,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 1,11</t>
+          <t>-11,48; 4,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 18,24</t>
+          <t>4,74; 18,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 13,88</t>
+          <t>0,55; 13,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 14,47</t>
+          <t>-28,01; -17,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,52; 21,94</t>
+          <t>10,28; 21,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 20,71</t>
+          <t>9,18; 20,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,37; 3,77</t>
+          <t>-19,44; -10,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,22</t>
+          <t>-17,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,3</t>
+          <t>-11,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 14,23</t>
+          <t>2,05; 14,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 7,33</t>
+          <t>-4,98; 7,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -0,99</t>
+          <t>-12,21; -0,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 8,28</t>
+          <t>-5,38; 8,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 2,03</t>
+          <t>-10,79; 2,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -11,28</t>
+          <t>-23,26; -11,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 10,16</t>
+          <t>0,8; 10,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 3,24</t>
+          <t>-5,7; 3,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,45; -7,52</t>
+          <t>-15,78; -7,75</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-15,98%</t>
+          <t>-17,44%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,85%</t>
+          <t>-33,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-24,81%</t>
+          <t>-25,57%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 39,61</t>
+          <t>4,84; 40,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 20,57</t>
+          <t>-11,8; 19,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,06; -2,61</t>
+          <t>-28,76; -1,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 16,41</t>
+          <t>-9,68; 17,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 3,91</t>
+          <t>-18,94; 4,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,37; -23,17</t>
+          <t>-41,08; -24,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 23,52</t>
+          <t>1,58; 23,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 7,45</t>
+          <t>-11,7; 7,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,22; -17,54</t>
+          <t>-32,81; -18,11</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,0</t>
+          <t>-8,5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,23</t>
+          <t>-17,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-12,59</t>
+          <t>-13,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,91</t>
+          <t>4,93; 9,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,61</t>
+          <t>1,78; 6,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -6,11</t>
+          <t>-11,15; -6,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,56</t>
+          <t>2,93; 7,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,32</t>
+          <t>-2,5; 2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,54; -4,32</t>
+          <t>-19,87; -15,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,15</t>
+          <t>4,75; 8,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,74</t>
+          <t>0,36; 3,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -8,04</t>
+          <t>-14,89; -11,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-20,77%</t>
+          <t>-17,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-23,86%</t>
+          <t>-27,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-22,44%</t>
+          <t>-23,26%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 21,39</t>
+          <t>10,11; 21,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 14,06</t>
+          <t>3,62; 14,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,35; -12,91</t>
+          <t>-22,68; -13,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 12,09</t>
+          <t>4,47; 12,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,71</t>
+          <t>-3,89; 3,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,36; -6,78</t>
+          <t>-30,32; -24,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 14,8</t>
+          <t>8,32; 14,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,79</t>
+          <t>0,63; 6,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,58; -14,26</t>
+          <t>-26,06; -20,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
